--- a/docs/test_report/ethfw_testreport_j721e.xlsx
+++ b/docs/test_report/ethfw_testreport_j721e.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table of Contents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Script Input Parameters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Test Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Test Percentage Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Test Plan | Execution Report" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Template Help" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Template Revision History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table of Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Script Input Parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Percentage Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Plan | Execution Report" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Help" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Revision History" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Test Plan | Execution Report'!$A$1:$U$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Plan | Execution Report'!$A$1:$U$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,54 +95,54 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -506,9 +506,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="10"/>
-    <col customWidth="1" max="2" min="2" width="35"/>
-    <col customWidth="1" max="3" min="3" width="80"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -658,10 +658,10 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -674,9 +674,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="35"/>
-    <col customWidth="1" max="2" min="2" width="35"/>
-    <col customWidth="1" max="3" min="3" width="35"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -709,12 +709,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2023-11-28 19:22:46.865862-06:00 CDT</t>
+          <t>2023-11-30 23:43:18.544360-06:00 CDT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -727,13 +727,13 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="26"/>
-    <col customWidth="1" max="2" min="2" width="26"/>
-    <col customWidth="1" max="3" min="3" width="26"/>
-    <col customWidth="1" max="4" min="4" width="26"/>
-    <col customWidth="1" max="5" min="5" width="26"/>
-    <col customWidth="1" max="6" min="6" width="26"/>
-    <col customWidth="1" max="7" min="7" width="26"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,7 +791,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1046,12 +1046,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="26"/>
-    <col customWidth="1" max="2" min="2" width="26"/>
-    <col customWidth="1" max="3" min="3" width="26"/>
-    <col customWidth="1" max="4" min="4" width="26"/>
-    <col customWidth="1" max="5" min="5" width="26"/>
-    <col customWidth="1" max="6" min="6" width="26"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1289,30 +1289,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U77"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="17"/>
-    <col customWidth="1" max="2" min="2" width="24"/>
-    <col customWidth="1" max="3" min="3" width="17"/>
-    <col customWidth="1" max="4" min="4" width="24"/>
-    <col customWidth="1" max="5" min="5" width="17"/>
-    <col customWidth="1" max="6" min="6" width="32"/>
-    <col customWidth="1" max="7" min="7" width="17"/>
-    <col customWidth="1" max="8" min="8" width="17"/>
-    <col customWidth="1" max="9" min="9" width="32"/>
-    <col customWidth="1" max="10" min="10" width="22"/>
-    <col customWidth="1" max="11" min="11" width="32"/>
-    <col customWidth="1" max="12" min="12" width="17"/>
-    <col customWidth="1" max="13" min="13" width="17"/>
-    <col customWidth="1" max="14" min="14" width="17"/>
-    <col customWidth="1" max="15" min="15" width="17"/>
-    <col customWidth="1" max="16" min="16" width="17"/>
-    <col customWidth="1" max="17" min="17" width="17"/>
-    <col customWidth="1" max="18" min="18" width="17"/>
-    <col customWidth="1" max="19" min="19" width="17"/>
-    <col customWidth="1" max="20" min="20" width="24"/>
-    <col customWidth="1" max="21" min="21" width="17"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform multicast and unicast tests to confirm HOL (head of line) blocking doesn't exist in switching
+          <t xml:space="preserve">Perform multicast and unicast tests to confirm HOL (head of line) blocking doesn't exist in switching
 </t>
         </is>
       </c>
@@ -2263,8 +2263,8 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>J721E or J7200 with Ethernet cables connected as follows:
-- J721E: MAC ports 3 and 8
+          <t>J721E or J7200 with Ethernet cables connected as follows:
+- J721E: MAC ports 3 and 8
 - J7200: MAC ports 2 and 3</t>
         </is>
       </c>
@@ -2359,14 +2359,14 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>This demo white-lists TCP and UDP protocols and hence blocking packets of other protocols in the VLAN network.
+          <t>This demo white-lists TCP and UDP protocols and hence blocking packets of other protocols in the VLAN network.
 Steps are documented in Ethernet Firmware Demo page: [https://software-dl.ti.com/jacinto7/esd/processor-sdk-rtos-jacinto7/latest/exports/docs/ethfw/docs/user_guide/demo_ethfw_combined_top.html#ethfw_ip_nxthdr_filtering]</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>J721E or J7200 with Ethernet cables connected as follows:
-- J721E: MAC ports 3 and 8
+          <t>J721E or J7200 with Ethernet cables connected as follows:
+- J721E: MAC ports 3 and 8
 - J7200: MAC ports 2 and 3</t>
         </is>
       </c>
@@ -2466,8 +2466,8 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>J721E or J7200 with Ethernet cables connected as follows:
-- J721E: MAC ports 3 and 8
+          <t>J721E or J7200 with Ethernet cables connected as follows:
+- J721E: MAC ports 3 and 8
 - J7200: MAC ports 2 and 3</t>
         </is>
       </c>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Validate PTP stack integration in Ethernet Firmware.
+          <t>Validate PTP stack integration in Ethernet Firmware.
 Steps are documented in Ethernet Firmware Demo page: https://software-dl.ti.com/jacinto7/esd/processor-sdk-rtos-jacinto7/latest/exports/docs/ethfw/docs/user_guide/demo_ethfw_combined_top.html#demo_ethfw_ptp_stack</t>
         </is>
       </c>
@@ -2662,15 +2662,15 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Validate ALE-based rate limiting feature in Ethernet Firmware.
-Rate Limiting can be enabled by adding a policer entry with parameters like Source and Destination MAC address of the traffic to be limited. The rate at which the traffic is limited is based on the values of Peak Information Rate (PIR) and Committed Information Rate (CIR) both in bits per second (bps) set in the policer entry.
+          <t>Validate ALE-based rate limiting feature in Ethernet Firmware.
+Rate Limiting can be enabled by adding a policer entry with parameters like Source and Destination MAC address of the traffic to be limited. The rate at which the traffic is limited is based on the values of Peak Information Rate (PIR) and Committed Information Rate (CIR) both in bits per second (bps) set in the policer entry.
 Steps are documented in Ethernet Firmware Demo page: https://software-dl.ti.com/jacinto7/esd/processor-sdk-rtos-jacinto7/latest/exports/docs/ethfw/docs/user_guide/demo_ethfw_combined_top.html</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>J721E or J7200 with Ethernet cables connected as follows:
-- J721E: MAC ports 3 and 8
+          <t>J721E or J7200 with Ethernet cables connected as follows:
+- J721E: MAC ports 3 and 8
 - J7200: MAC ports 2 and 3</t>
         </is>
       </c>
@@ -2773,9 +2773,9 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Run SW InterVLAN routing with GESI/QSGMII ports.
-Demonstrate performance w.r.t. below params
- # Packet per second
+          <t>Run SW InterVLAN routing with GESI/QSGMII ports.
+Demonstrate performance w.r.t. below params
+ # Packet per second
  # CPU load</t>
         </is>
       </c>
@@ -2880,8 +2880,8 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -2981,8 +2981,8 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3077,14 +3077,14 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>SafeRTOS cores (MCU2_0 and MCU2_1) running Ethernet firmware should be able to send and receive packets through TCP/UDP/ICMP/IP using integrated inter-core Ethernet driver and lwIP bridge.
-This is demonstrated by running EthFW server and client on R5F0 and R5F1 respectively and making sure that EthFW client on R5F1 is able to get IP address assigned by the external DHCP server.
+          <t>SafeRTOS cores (MCU2_0 and MCU2_1) running Ethernet firmware should be able to send and receive packets through TCP/UDP/ICMP/IP using integrated inter-core Ethernet driver and lwIP bridge.
+This is demonstrated by running EthFW server and client on R5F0 and R5F1 respectively and making sure that EthFW client on R5F1 is able to get IP address assigned by the external DHCP server.
 This process involves broadcast packets (DHCP discover, ARP broadcast ) from the R5F1 client to be routed through the client and server lwIP bridge and inter-core drivers to the external DHCP server thus verifying inter-core Ethernet communication between RTOS cores.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>- J721E EVM, J7200 EVM or J784S4 EVM
+          <t>- J721E EVM, J7200 EVM or J784S4 EVM
 - Linux PC</t>
         </is>
       </c>
@@ -3179,13 +3179,13 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>The tap device on A72 Linux, which is created by running the Tap application provided in the SDK, should be able able to send and receive packets with and external PC as well as R5F cores through TCP/UDP/ICMP/IP via inter-core Ethernet and lwIP bridge integrated in the EthFW server on R5F0.
+          <t>The tap device on A72 Linux, which is created by running the Tap application provided in the SDK, should be able able to send and receive packets with and external PC as well as R5F cores through TCP/UDP/ICMP/IP via inter-core Ethernet and lwIP bridge integrated in the EthFW server on R5F0.
 This is demonstrated by running EthFW server and Tap application on R5F0 and A72 Linux respectively, and making sure that Tap device on A72 Linux is able to get IP address assigned by the external DHCP server and ping both the RTOS cores as well using their respective IP addresses.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>- J721E EVM, J7200 EVM or J784S4 EVM.
+          <t>- J721E EVM, J7200 EVM or J784S4 EVM.
 - Linux PC</t>
         </is>
       </c>
@@ -3285,8 +3285,8 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3386,8 +3386,8 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 -J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3487,8 +3487,8 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3588,8 +3588,8 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3689,8 +3689,8 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3790,8 +3790,8 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
-- J7200 EVM with QSGMII expansion card
+          <t>- J7 EVM with GESI expansion card
+- J7200 EVM with QSGMII expansion card
 - J784S4 EVM with QSGMII expansion card</t>
         </is>
       </c>
@@ -3891,13 +3891,13 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM with GESI expansion card
+          <t>- J7 EVM with GESI expansion card
 - J7200 EVM with QSGMII expansion card</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>1. An ALE policer should be created for remote core's flowIdx for exclusive multicast request.
+          <t>1. An ALE policer should be created for remote core's flowIdx for exclusive multicast request.
 2. Shared multicast requests should result in an update of EthFw's bridge FDB.</t>
         </is>
       </c>
@@ -3987,13 +3987,13 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>The tap device on A72 Linux, which is created by running the Tap application provided in the SDK, should be able able to send and receive packets with and external PC as well as R5F cores through TCP/UDP/ICMP/IP via inter-core Ethernet and lwIP bridge integrated in the EthFW server on R5F0.
+          <t>The tap device on A72 Linux, which is created by running the Tap application provided in the SDK, should be able able to send and receive packets with and external PC as well as R5F cores through TCP/UDP/ICMP/IP via inter-core Ethernet and lwIP bridge integrated in the EthFW server on R5F0.
 This is demonstrated by running EthFW server and Tap application on R5F0 and A72 Linux respectively, and making sure that Tap device on A72 Linux is able to get IP address assigned by the external DHCP server and ping both the RTOS cores as well using their respective IP addresses.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>- J721E EVM, J7200 EVM or J784S4 EVM.
+          <t>- J721E EVM, J7200 EVM or J784S4 EVM.
 - Linux PC</t>
         </is>
       </c>
@@ -4088,14 +4088,14 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>RTOS cores (MCU2_0 and MCU2_1) running Ethernet firmware should be able to send and receive packets through TCP/UDP/ICMP/IP using integrated inter-core Ethernet driver and lwIP bridge.
-This is demonstrated by running EthFW server and client on R5F0 and R5F1 respectively and making sure that EthFW client on R5F1 is able to get IP address assigned by the external DHCP server.
+          <t>RTOS cores (MCU2_0 and MCU2_1) running Ethernet firmware should be able to send and receive packets through TCP/UDP/ICMP/IP using integrated inter-core Ethernet driver and lwIP bridge.
+This is demonstrated by running EthFW server and client on R5F0 and R5F1 respectively and making sure that EthFW client on R5F1 is able to get IP address assigned by the external DHCP server.
 This process involves broadcast packets (DHCP discover, ARP broadcast ) from the R5F1 client to be routed through the client and server lwIP bridge and inter-core drivers to the external DHCP server thus verifying inter-core Ethernet communication between RTOS cores.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>J721E EVM or J7200 EVM
+          <t>J721E EVM or J7200 EVM
 Linux PC</t>
         </is>
       </c>
@@ -4150,26 +4150,34 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2283</t>
+          <t>ETHFW-2370</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>EthFw gPTP Test Plan</t>
+          <t>ETHFW Thin Clients Test Plan</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2274</t>
+          <t>ETHFW-2537</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>EthFw: TSN: gPTP: Master mode</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+          <t>ETHFW: Promiscuous mode on MAC-only port (Linux)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-1711</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
           <t>j721e-evm,j7200-evm,j784s4-evm</t>
@@ -4177,39 +4185,23 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Verify that gPTP stack integrated in ETHFW can run as master.
-Testing between two EVMs: (Recommended)
- # Force ETHFW gPTP (DUT) to run as master set CONF_PRIMARY_PRIORITY1 240 using gptpconf_set_item(). If not forcing DUT to be master, DUT can be master/slave.
- # Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.
-                                                                                 OR
-Testing between EVM and a PC: (Recommended on Intel i210 card)
-        1. Configure gptp2.conf CONF_PRIMARY_PRIORITY1 255 to make PC become slave.
-        2. Run gptp2d on the PC side.
-        3. Check the log from DUT (master) and PC (slave).
-Master logs:
-{code:java}
-GM changed old=00:00:00:00:00:00:00:00, new=70:FF:76:FF:FE:1D:E1:A0{code}
-{code:java}
-domain=0, offset=0nsec, hw-adjrate=0ppb
-            gmsync=true, last_setts64=0nsec ..{code}</t>
+          <t>Test that CPSW ALE can be set in promiscuous mode and that all traffic is forwarded to the host port.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1. Force ETHFW gPTP to run as master by setting CONF_PRIMARY_PRIORITY1 240 using gptpconf_set_item(). If DUT is not forced as master, it could run as either master or slave depending on the connected device.
-2. Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.</t>
+          <t>J721E/J7200/J784S4 EVM
+Linux PC</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>"GM changed old=00:00:00:00:00:00:00:00, new=70:FF:76:FF:FE:1D:E1:A0"
-domain=0, offset=0nsec, hw-adjrate=0ppb
-            gmsync=true, last_setts64=0nsec ..</t>
+          <t>Ping/Iperf should work fine</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4229,7 +4221,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Regression,Sanity</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4247,11 +4239,19 @@
           <t>ETHFW 9.1 Release Test Run (j721e)</t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
-      <c r="U29" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2536</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t>VLAN tagged packets coming on MAC-only port in promiscuous mode</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2282</t>
+          <t>ETHFW-2274</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>EthFw: TSN: gPTP: Slave mode</t>
+          <t>EthFw: TSN: gPTP: Master mode</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
@@ -4290,36 +4290,34 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Verify that gPTP stack integrated in ETHFW can run as slave.
-Testing between two EVMs: (Recommended)
- # Force ETHFW gPTP (DUT) to run as slave by setting CONF_PRIMARY_PRIORITY1 255 using gptpconf_set_item().
- ## If not forcing DUT to be slave, DUT can be master or slave.
- # Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.
-                                                                                             OR
-Testing between EVM and PC: (Recommended on Intel i210 card)
-        1. Configure gptp2.conf CONF_PRIMARY_PRIORITY1 240 to make PC become master.
-        2. Run gptp2d on the PC side
-        3. Check the log from DUT (slave) and PC(master)
-Slave logs (when second EVM becomes new GM):
-{code:java}
-GM changed old=24:76:25:FF:FE:96:6C:41, new=70:FF:76:FF:FE:1D:9B:77{code}
-here the machine with MAC address: 70:FF:76:FF:FE:1D:9B:77 is the master
-After a while, DUT will keep printing repeatedly the clock rate without switching GM:
-{code:java}
-INF:gptp:domainNumber=0, clock_master_sync_receive:the master clock rate to &lt;number&gt;ppb{code}</t>
+          <t>Verify that gPTP stack integrated in ETHFW can run as master.
+Testing between two EVMs: (Recommended)
+ # Force ETHFW gPTP (DUT) to run as master set CONF_PRIMARY_PRIORITY1 240 using gptpconf_set_item(). If not forcing DUT to be master, DUT can be master/slave.
+ # Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.
+                                                                                 OR
+Testing between EVM and a PC: (Recommended on Intel i210 card)
+        1. Configure gptp2.conf CONF_PRIMARY_PRIORITY1 255 to make PC become slave.
+        2. Run gptp2d on the PC side.
+        3. Check the log from DUT (master) and PC (slave).
+Master logs:
+{code:java}
+GM changed old=00:00:00:00:00:00:00:00, new=70:FF:76:FF:FE:1D:E1:A0{code}
+{code:java}
+domain=0, offset=0nsec, hw-adjrate=0ppb
+            gmsync=true, last_setts64=0nsec ..{code}</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1. Force ETHFW gPTP (DUT) to run as slave set CONF_PRIMARY_PRIORITY1 255 using gptpconf_set_item(). 3. If not forcing DUT to be slave, DUT can be master/slave.
+          <t>1. Force ETHFW gPTP to run as master by setting CONF_PRIMARY_PRIORITY1 240 using gptpconf_set_item(). If DUT is not forced as master, it could run as either master or slave depending on the connected device.
 2. Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>1. When DUT switches roles from GM to slave, DUT logs should show "GM changed old=24:76:25:FF:FE:96:6C:41, new=70:FF:76:FF:FE:1D:9B:77". Here new GM's MAC address is: 70:FF:76:FF:FE:1D:9B:77.
-2. After a while, DUT will keep printing repeatedly the clock rate without switching GM:  "INF:gptp:domainNumber=0, clock_master_sync_receive:the master clock rate to &lt;number&gt;ppb"
-3. PC will not show clock rate adjustment log.</t>
+          <t>"GM changed old=00:00:00:00:00:00:00:00, new=70:FF:76:FF:FE:1D:E1:A0"
+domain=0, offset=0nsec, hw-adjrate=0ppb
+            gmsync=true, last_setts64=0nsec ..</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4378,12 +4376,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2275</t>
+          <t>ETHFW-2282</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>EthFw: TSN: gPTP: Master-slave reliability</t>
+          <t>EthFw: TSN: gPTP: Slave mode</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
@@ -4400,20 +4398,36 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>1. Keep master (ETHFW-2274) and slave (ETHFW-2282) running 2 hours
-2. Check if the DUT is crashed or not</t>
+          <t>Verify that gPTP stack integrated in ETHFW can run as slave.
+Testing between two EVMs: (Recommended)
+ # Force ETHFW gPTP (DUT) to run as slave by setting CONF_PRIMARY_PRIORITY1 255 using gptpconf_set_item().
+ ## If not forcing DUT to be slave, DUT can be master or slave.
+ # Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.
+                                                                                             OR
+Testing between EVM and PC: (Recommended on Intel i210 card)
+        1. Configure gptp2.conf CONF_PRIMARY_PRIORITY1 240 to make PC become master.
+        2. Run gptp2d on the PC side
+        3. Check the log from DUT (slave) and PC(master)
+Slave logs (when second EVM becomes new GM):
+{code:java}
+GM changed old=24:76:25:FF:FE:96:6C:41, new=70:FF:76:FF:FE:1D:9B:77{code}
+here the machine with MAC address: 70:FF:76:FF:FE:1D:9B:77 is the master
+After a while, DUT will keep printing repeatedly the clock rate without switching GM:
+{code:java}
+INF:gptp:domainNumber=0, clock_master_sync_receive:the master clock rate to &lt;number&gt;ppb{code}</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Connect two devices running ETHFW, one device as master and another as slave.
-For the device in master mode, refer to test setup instructions in ETHFW-2274.
-For the device in slave mode, refer to test setup instructions in ETHFW-2282.</t>
+          <t>1. Force ETHFW gPTP (DUT) to run as slave set CONF_PRIMARY_PRIORITY1 255 using gptpconf_set_item(). 3. If not forcing DUT to be slave, DUT can be master/slave.
+2. Connect DUT to another EVM running ETHFW example via MAC port 3 on both boards.</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>ETHFW application continues to run properly and the two devices (master and slave) are still synchronized.</t>
+          <t>1. When DUT switches roles from GM to slave, DUT logs should show "GM changed old=24:76:25:FF:FE:96:6C:41, new=70:FF:76:FF:FE:1D:9B:77". Here new GM's MAC address is: 70:FF:76:FF:FE:1D:9B:77.
+2. After a while, DUT will keep printing repeatedly the clock rate without switching GM:  "INF:gptp:domainNumber=0, clock_master_sync_receive:the master clock rate to &lt;number&gt;ppb"
+3. PC will not show clock rate adjustment log.</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4472,12 +4486,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2281</t>
+          <t>ETHFW-2275</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>EthFw: TSN: gPTP: Disconnect/re-connect in master mode</t>
+          <t>EthFw: TSN: gPTP: Master-slave reliability</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
@@ -4494,19 +4508,20 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Verifies that gPTP stack integrated in ETHFW continues to work properly as a master after cable disconnect/reconnect, and synchronize with the connected device.</t>
+          <t>1. Keep master (ETHFW-2274) and slave (ETHFW-2282) running 2 hours
+2. Check if the DUT is crashed or not</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Refer to ETHFW slave test setup described in ETHFW-2274.</t>
+          <t>Connect two devices running ETHFW, one device as master and another as slave.
+For the device in master mode, refer to test setup instructions in ETHFW-2274.
+For the device in slave mode, refer to test setup instructions in ETHFW-2282.</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>DUT shows the disconnected log like this: "INF:gptp:gptpnet_cb_devdown:portIndex=1", and the clock rate log will disappear on the PC side.
-After reconnecting: DUT show log like this "INF:gptp:index=1 speed=1000, duplex=full, ptpdev=tilld0", and works as master. 
-The result should be as mentioned in ETHFW-2274</t>
+          <t>ETHFW application continues to run properly and the two devices (master and slave) are still synchronized.</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4565,12 +4580,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2376</t>
+          <t>ETHFW-2281</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>EthFw: TSN: gPTP: Disconnect/re-connected in slave mode</t>
+          <t>EthFw: TSN: gPTP: Disconnect/re-connect in master mode</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
@@ -4587,18 +4602,19 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Verifies that gPTP stack integrated in ETHFW continues to work properly as slave after cable disconnect/reconnect, and synchronize with the connected device.</t>
+          <t>Verifies that gPTP stack integrated in ETHFW continues to work properly as a master after cable disconnect/reconnect, and synchronize with the connected device.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Refer to ETHFW slave test setup described in ETHFW-2282.</t>
+          <t>Refer to ETHFW slave test setup described in ETHFW-2274.</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>DUT shows the disconnected log like this: "INF:gptp:gptpnet_cb_devdown:portIndex=1", and the clock rate log will disappear
-After reconnecting, DUT works as slave and the result should be same as the mentioned in ETHFW-2282.</t>
+          <t>DUT shows the disconnected log like this: "INF:gptp:gptpnet_cb_devdown:portIndex=1", and the clock rate log will disappear on the PC side.
+After reconnecting: DUT show log like this "INF:gptp:index=1 speed=1000, duplex=full, ptpdev=tilld0", and works as master. 
+The result should be as mentioned in ETHFW-2274</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -4647,34 +4663,26 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2366</t>
+          <t>ETHFW-2283</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 9.x Release Test Plan (j721e)</t>
+          <t>EthFw gPTP Test Plan</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2124</t>
+          <t>ETHFW-2376</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EthFw: SafeRTOS: Static IP test </t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>ETHFW-2115</t>
-        </is>
-      </c>
+          <t>EthFw: TSN: gPTP: Disconnect/re-connected in slave mode</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>j721e-evm,j7200-evm,j784s4-evm</t>
@@ -4682,25 +4690,23 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware built for SafeRTOS with static IP address tests.</t>
+          <t>Verifies that gPTP stack integrated in ETHFW continues to work properly as slave after cable disconnect/reconnect, and synchronize with the connected device.</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>- J7 EVM, J7200 EVM or J784S4 EVM
-- GESI board (J721E) or QSGMII board (J7200, J748S4)
-- PC</t>
+          <t>Refer to ETHFW slave test setup described in ETHFW-2282.</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>* eth1 interface should get a dynamic IP address and ping to this address should work fine.
-* eth1 interface should be able to pass static IP and ping to this address should work fine.</t>
+          <t>DUT shows the disconnected log like this: "INF:gptp:gptpnet_cb_devdown:portIndex=1", and the clock rate log will disappear
+After reconnecting, DUT works as slave and the result should be same as the mentioned in ETHFW-2282.</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4710,7 +4716,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Customer Usage</t>
+          <t>Requirements-Analysis</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4720,7 +4726,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression,Sanity</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4759,12 +4765,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2233</t>
+          <t>ETHFW-2124</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Boot time benchmark</t>
+          <t xml:space="preserve">EthFw: SafeRTOS: Static IP test </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4774,7 +4780,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1964</t>
+          <t>ETHFW-2115</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4789,34 +4795,30 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Test that Linux client application can enable a virtual MAC interface configured in MAC-only mode.</t>
+          <t>Ethernet Firmware built for SafeRTOS with static IP address tests.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>EVM #1 running ETHFW should be as follows:
-- J7 EVM with GESI expansion + QSGMII expansion cards
-- J7200 EVM with QSGMII expansion card
-- J784S4 EVM with QSGMII expansion card
-EVM #2 is needed which will run Enet LLD lwIP as described in the following testcases:
-- J721E: See setup in testcase ETHFW-2065.
-- J7200: See setup in testcase ETHFW-2067.
-- J784S4: See setup in testcase ETHFW-2071.</t>
+          <t>- J7 EVM, J7200 EVM or J784S4 EVM
+- GESI board (J721E) or QSGMII board (J7200, J748S4)
+- PC</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>ETHFW boot time shall be printed in console.</t>
+          <t>* eth1 interface should get a dynamic IP address and ping to this address should work fine.
+* eth1 interface should be able to pass static IP and ping to this address should work fine.</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Requirements-Analysis</t>
+          <t>Customer Usage</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -4865,22 +4867,22 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2010</t>
+          <t>ETHFW-2233</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Standalone test with CCS boot</t>
+          <t>EthFw: Boot time benchmark</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1947,ETHFW-1952</t>
+          <t>ETHFW-1964</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4895,31 +4897,29 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware should be able to run with CCS boot and enable the MAC ports as follows:
- * J721E: All 8 MAC ports.
- * J7200: All 4 MAC ports.
- * J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).
- Refer to EthFw User's Guide for port mode allocation (switch mode vs MAC-only mode).
-EthFw shall be able to acquire an IP address from network.</t>
+          <t>Test that Linux client application can enable a virtual MAC interface configured in MAC-only mode.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>J721E/J7200/J784S4 EVM
-Linux PC</t>
+          <t>EVM #1 running ETHFW should be as follows:
+- J7 EVM with GESI expansion + QSGMII expansion cards
+- J7200 EVM with QSGMII expansion card
+- J784S4 EVM with QSGMII expansion card
+EVM #2 is needed which will run Enet LLD lwIP as described in the following testcases:
+- J721E: See setup in testcase ETHFW-2065.
+- J7200: See setup in testcase ETHFW-2067.
+- J784S4: See setup in testcase ETHFW-2071.</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>EthFw should be able to successfully initialize and configure the MAC ports enabled for the given SoC.
-J721E: All 8 MAC ports.
-J7200: All 4 MAC ports.
-J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).</t>
+          <t>ETHFW boot time shall be printed in console.</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2009</t>
+          <t>ETHFW-2010</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Standalone test with SBL boot</t>
+          <t>EthFw: Standalone test with CCS boot</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1952,ETHFW-1947</t>
+          <t>ETHFW-1947,ETHFW-1952</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5003,25 +5003,25 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware should be able to run with SBL boot and enable the MAC ports as follows:
- * J721E: All 8 MAC ports.
- * J7200: All 4 MAC ports.
- * J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).
- Refer to EthFw User's Guide for port mode allocation (switch mode vs MAC-only mode).
+          <t>Ethernet Firmware should be able to run with CCS boot and enable the MAC ports as follows:
+ * J721E: All 8 MAC ports.
+ * J7200: All 4 MAC ports.
+ * J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).
+ Refer to EthFw User's Guide for port mode allocation (switch mode vs MAC-only mode).
 EthFw shall be able to acquire an IP address from network.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>J721E/J7200/J784S4 EVM
+          <t>J721E/J7200/J784S4 EVM
 Linux PC</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>EthFw should be able to successfully initialize and configure the MAC ports enabled for the given SoC.
-J721E: All 8 MAC ports.
-J7200: All 4 MAC ports.
+          <t>EthFw should be able to successfully initialize and configure the MAC ports enabled for the given SoC.
+J721E: All 8 MAC ports.
+J7200: All 4 MAC ports.
 J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).</t>
         </is>
       </c>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1663</t>
+          <t>ETHFW-2009</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>EthFw - QSGMII - Enable SERDES sharing in EthFw</t>
+          <t>EthFw: Standalone test with SBL boot</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-607,ETHFW-1920</t>
+          <t>ETHFW-1952,ETHFW-1947</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>j721e-evm,j7200-evm</t>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5111,24 +5111,26 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enable SERDES in multi-link mode with Linux boot flow. 
-For J721E
-- EthFw should use QSGMII on SERDES0 lane 1 (SGMII1) (
-- Linux should use PCIE on SERDES0 lane 0 
-For J7200
-- EthFw should use QSGMII on Port 0 – SERDES0 Lane 2 
-- Linux should use PCIE and other peripherals on other lanes 
- </t>
+          <t>Ethernet Firmware should be able to run with SBL boot and enable the MAC ports as follows:
+ * J721E: All 8 MAC ports.
+ * J7200: All 4 MAC ports.
+ * J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).
+ Refer to EthFw User's Guide for port mode allocation (switch mode vs MAC-only mode).
+EthFw shall be able to acquire an IP address from network.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t>J721E/J7200/J784S4 EVM
+Linux PC</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware server app should execute successfully.</t>
+          <t>EthFw should be able to successfully initialize and configure the MAC ports enabled for the given SoC.
+J721E: All 8 MAC ports.
+J7200: All 4 MAC ports.
+J784S4: 4 MAC ports in QSGMII expansion board + 1 MAC port in bridge board (optional).</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5153,7 +5155,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>CPSW</t>
+          <t>EthFw</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5187,27 +5189,27 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1823</t>
+          <t>ETHFW-1663</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EthFw: lwIP Integration </t>
+          <t>EthFw - QSGMII - Enable SERDES sharing in EthFw</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1966,ETHFW-1953,ETHFW-1912,ETHFW-1950,ETHFW-1718,ETHFW-1716,ETHFW-1742</t>
+          <t>ETHFW-607,ETHFW-1920</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+          <t>j721e-evm,j7200-evm</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5217,19 +5219,24 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware should be able to send and receive packets through TCP/UDP/ICMP/IP using integrated lwIP stack.
-lwIP integration validation also verifies FreeRTOS integration.</t>
+          <t xml:space="preserve">Enable SERDES in multi-link mode with Linux boot flow. 
+For J721E
+- EthFw should use QSGMII on SERDES0 lane 1 (SGMII1) (
+- Linux should use PCIE on SERDES0 lane 0 
+For J7200
+- EthFw should use QSGMII on Port 0 – SERDES0 Lane 2 
+- Linux should use PCIE and other peripherals on other lanes 
+ </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>J721E EVM, J7200 EVM or J784S4 EVM
-Linux PC</t>
+          <t>J7 EVM with GESI Expansion card</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>EthFw should be able to successfully establish a connection with an external device, acquire IP address and exchange packets.</t>
+          <t>Ethernet Firmware server app should execute successfully.</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5254,7 +5261,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>EthFw</t>
+          <t>CPSW</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -5288,27 +5295,27 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1701</t>
+          <t>ETHFW-1823</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>[EthFw] Windows build support</t>
+          <t xml:space="preserve">EthFw: lwIP Integration </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1686,ETHFW-1742</t>
+          <t>ETHFW-1966,ETHFW-1953,ETHFW-1912,ETHFW-1950,ETHFW-1718,ETHFW-1716,ETHFW-1742</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>j721e-evm,j7200-evm</t>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5318,21 +5325,19 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Build EthFw separately for J7200 and J721E in a Windows PC.</t>
+          <t>Ethernet Firmware should be able to send and receive packets through TCP/UDP/ICMP/IP using integrated lwIP stack.
+lwIP integration validation also verifies FreeRTOS integration.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Windows PC and Processor SDK release package.</t>
+          <t>J721E EVM, J7200 EVM or J784S4 EVM
+Linux PC</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>The following EthFw images shall be built:
-* EthFw image for CCS with symbols
-* EthFw image for Linux/QNX with symbols
-* EthFw image for CCS without symbols (_strip.xer5f file)
-* EthFw image for Linux/QNX without symbols (_strip.xer5f file)</t>
+          <t>EthFw should be able to successfully establish a connection with an external device, acquire IP address and exchange packets.</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -5372,9 +5377,9 @@
       </c>
       <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="10" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="U40" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5391,22 +5396,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1551</t>
+          <t>ETHFW-1701</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][Protocol]Protocol: Switch resident protocol:802.1AS rev support</t>
+          <t>[EthFw] Windows build support</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1293</t>
+          <t>ETHFW-1686,ETHFW-1742</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -5421,17 +5426,21 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Protocol:802.1AS rev support</t>
+          <t>Build EthFw separately for J7200 and J721E in a Windows PC.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  J7 EVM with GESI or QSGMII Expansion card </t>
+          <t>Windows PC and Processor SDK release package.</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>ETHFW running on mcu2_0 should synchronize with Master running on PC</t>
+          <t>The following EthFw images shall be built:
+* EthFw image for CCS with symbols
+* EthFw image for Linux/QNX with symbols
+* EthFw image for CCS without symbols (_strip.xer5f file)
+* EthFw image for Linux/QNX without symbols (_strip.xer5f file)</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -5451,7 +5460,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5471,9 +5480,9 @@
       </c>
       <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U41" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -5490,22 +5499,22 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1355</t>
+          <t>ETHFW-1551</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][Packaging] The ethernet firmware shall be hosted in a separate repo to support firmware only release decoupled from rest of Processor SDK</t>
+          <t>[EthFW][Protocol]Protocol: Switch resident protocol:802.1AS rev support</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1290,ETHFW-1135</t>
+          <t>ETHFW-1293</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5520,31 +5529,27 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ethernet firmware shall be hosted in a separate repo to support firmware only release decoupled from rest of Processor SDK
-This will require ethernet firmware to have independent release plan (and version plan) decoupled from Processor SDK PDK
-This is needed to allow LCPD to consume CPSW Ethernet switch firmware without waiting for Processor SDK RTOS  </t>
+          <t>Protocol:802.1AS rev support</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t xml:space="preserve">  J7 EVM with GESI or QSGMII Expansion card </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>1. separate package for ethfw
-2. should be available at external git.ti.com
-3. should be released under TI-TFL license</t>
+          <t>ETHFW running on mcu2_0 should synchronize with Master running on PC</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Customer Usage</t>
+          <t>Requirements-Analysis</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5554,7 +5559,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5593,12 +5598,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1010</t>
+          <t>ETHFW-1355</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC: All cores must allocate cores own MAC Address/IP address by sending msg to central IP/MAC resource manager running on master core</t>
+          <t>[EthFW][Packaging] The ethernet firmware shall be hosted in a separate repo to support firmware only release decoupled from rest of Processor SDK</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -5608,7 +5613,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1288,ETHFW-2172</t>
+          <t>ETHFW-1290,ETHFW-1135</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5623,7 +5628,9 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>IPC: All cores must allocate cores own MAC Address/IP address by sending msg to central IP/MAC resource manager running on master core</t>
+          <t xml:space="preserve">The ethernet firmware shall be hosted in a separate repo to support firmware only release decoupled from rest of Processor SDK
+This will require ethernet firmware to have independent release plan (and version plan) decoupled from Processor SDK PDK
+This is needed to allow LCPD to consume CPSW Ethernet switch firmware without waiting for Processor SDK RTOS  </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5633,17 +5640,19 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">All core must register them self by sending msg to master core </t>
+          <t>1. separate package for ethfw
+2. should be available at external git.ti.com
+3. should be released under TI-TFL license</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Requirements-Analysis</t>
+          <t>Customer Usage</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -5692,22 +5701,22 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1542</t>
+          <t>ETHFW-1010</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>[CPSW][System]Timesynch:Forward Timesync event to other registered cores</t>
+          <t>[EthFw][IPC]IPC: All cores must allocate cores own MAC Address/IP address by sending msg to central IP/MAC resource manager running on master core</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1287</t>
+          <t>ETHFW-1288,ETHFW-2172</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5722,17 +5731,17 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Timesynch:Forward Timesync event to other registered cores</t>
+          <t>IPC: All cores must allocate cores own MAC Address/IP address by sending msg to central IP/MAC resource manager running on master core</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J7 EVM with GESI or QSGMII Expansion card </t>
+          <t>J7 EVM with GESI Expansion card</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Remote client running on mcu2_1 should be able to receive CPTS hardware push notifications and able to synchronize with grandmaster using event information.</t>
+          <t xml:space="preserve">All core must register them self by sending msg to master core </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -5752,7 +5761,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5791,22 +5800,22 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1094</t>
+          <t>ETHFW-1542</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC:Remote core invocation APIs for switch config should be stateless on remote core side</t>
+          <t>[CPSW][System]Timesynch:Forward Timesync event to other registered cores</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1280,ETHFW-2172</t>
+          <t>ETHFW-1287</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -5821,17 +5830,17 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>IPC:Remote core invocation APIs for switch config should be stateless on remote core side</t>
+          <t>Timesynch:Forward Timesync event to other registered cores</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t xml:space="preserve"> J7 EVM with GESI or QSGMII Expansion card </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>client side application does not aware of state</t>
+          <t>Remote client running on mcu2_1 should be able to receive CPTS hardware push notifications and able to synchronize with grandmaster using event information.</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -5851,7 +5860,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5890,22 +5899,22 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1545</t>
+          <t>ETHFW-1094</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][Linux] Ethfw binary should have fixed UART ID assigned for console output</t>
+          <t>[EthFw][IPC]IPC:Remote core invocation APIs for switch config should be stateless on remote core side</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1253</t>
+          <t>ETHFW-1280,ETHFW-2172</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5920,21 +5929,17 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Ethfw binary should have fixed UART ID assigned for console output (debugging) for each supported platform.
-It's required for proper DT configuration - UART used by EthFW has to be disabled in DT for Linux.
-j721e - UART 2, serial@2820000</t>
+          <t>IPC:Remote core invocation APIs for switch config should be stateless on remote core side</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">mcu2_0  - app_remoteswitchcfg_server.xer5f 
-</t>
+          <t>J7 EVM with GESI Expansion card</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EthFw should initialize and print the logs including version info on Main domain UART instance 2 (UART2)
-</t>
+          <t>client side application does not aware of state</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -5954,7 +5959,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5993,22 +5998,22 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1030</t>
+          <t>ETHFW-1545</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC: Initial handshake and CPSW init completion notification</t>
+          <t>[EthFw][Linux] Ethfw binary should have fixed UART ID assigned for console output</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1245,ETHFW-2170</t>
+          <t>ETHFW-1253</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -6023,19 +6028,21 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>IPC: Sync mechanism
-  Initial shared memory based handshake
-  Notification to remote cores on CPSW initial configuration completion</t>
+          <t>Ethfw binary should have fixed UART ID assigned for console output (debugging) for each supported platform.
+It's required for proper DT configuration - UART used by EthFW has to be disabled in DT for Linux.
+j721e - UART 2, serial@2820000</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t xml:space="preserve">mcu2_0  - app_remoteswitchcfg_server.xer5f 
+</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">After successfully CPSW initialization, notification send to all remote cores </t>
+          <t xml:space="preserve">EthFw should initialize and print the logs including version info on Main domain UART instance 2 (UART2)
+</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -6055,7 +6062,7 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -6094,27 +6101,27 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2367</t>
+          <t>ETHFW-1030</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][Packaging] TI TSPA License</t>
+          <t>[EthFw][IPC]IPC: Initial handshake and CPSW init completion notification</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1237</t>
+          <t>ETHFW-1245,ETHFW-2170</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+          <t>j721e-evm,j7200-evm</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -6124,27 +6131,29 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Verify that Ethernet Firmware source files are released under TI Text File License (TSPA).</t>
+          <t>IPC: Sync mechanism
+  Initial shared memory based handshake
+  Notification to remote cores on CPSW initial configuration completion</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>ETHFW repository with source code.</t>
+          <t>J7 EVM with GESI Expansion card</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>All source files shall have TI TSPA license header.</t>
+          <t xml:space="preserve">After successfully CPSW initialization, notification send to all remote cores </t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Customer Usage</t>
+          <t>Requirements-Analysis</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -6193,12 +6202,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1552</t>
+          <t>ETHFW-2367</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][System]Protocol: ARP/RARP protocol database: Single Core must maintain ARP entries for MAC/IP address assigned to other cores</t>
+          <t>[EthFW][Packaging] TI TSPA License</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -6208,7 +6217,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1229</t>
+          <t>ETHFW-1237</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -6223,33 +6232,27 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Protocol: ARP/RARP protocol
- Protocol: ARP/RARP protocol database: Single Core must maintain ARP entries for MAC/IP address assigned to other cores
-In CPSW9G, the broadcast and multicast traffic can be handled by only single core and EthFw handles it. So all broadcast packets are received by only EthFw. Virtual clients only receive unicast packets with MAC address assigned to it.
-Due to this limitation, the ARP requests for remote clients which are broadcast packets can’t be received by remote clients hence it can’t communication with external world.
-To avoid this, remote clients should register their IP with EthFW/R5 which serves the ARP requests on remote clients behalf and EthFw should maintain these ARP entries.
-Now once the external communicating entity has MAC address for QNX, it sends direct unicast packets which are anyway are directly received on remote clients.</t>
+          <t>Verify that Ethernet Firmware source files are released under TI Text File License (TSPA).</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">J7 EVM with GESI or QSGMII Expansion card
-</t>
+          <t>ETHFW repository with source code.</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Remote client running on mcu2_1 should be able to register IP address with EthFw. Ping from PC to remote client should work</t>
+          <t>All source files shall have TI TSPA license header.</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Requirements-Analysis</t>
+          <t>Customer Usage</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -6259,7 +6262,7 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -6298,27 +6301,27 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1331</t>
+          <t>ETHFW-1552</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC:All CPSW subsystem register setting shall be done by means of IPC message to switch R5 core.Not direct register config shall be done on remote cores.</t>
+          <t>[EthFW][System]Protocol: ARP/RARP protocol database: Single Core must maintain ARP entries for MAC/IP address assigned to other cores</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1203,ETHFW-2170</t>
+          <t>ETHFW-1229</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>j721e-evm,j7200-evm</t>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6328,17 +6331,23 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>IPC:All CPSW subsystem register setting shall be done by means of IPC message to switch R5 core.Not direct register config shall be done on remote cores.</t>
+          <t>Protocol: ARP/RARP protocol
+ Protocol: ARP/RARP protocol database: Single Core must maintain ARP entries for MAC/IP address assigned to other cores
+In CPSW9G, the broadcast and multicast traffic can be handled by only single core and EthFw handles it. So all broadcast packets are received by only EthFw. Virtual clients only receive unicast packets with MAC address assigned to it.
+Due to this limitation, the ARP requests for remote clients which are broadcast packets can’t be received by remote clients hence it can’t communication with external world.
+To avoid this, remote clients should register their IP with EthFW/R5 which serves the ARP requests on remote clients behalf and EthFw should maintain these ARP entries.
+Now once the external communicating entity has MAC address for QNX, it sends direct unicast packets which are anyway are directly received on remote clients.</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI or QSGMII DB</t>
+          <t xml:space="preserve">J7 EVM with GESI or QSGMII Expansion card
+</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>&lt;To be updated&gt;</t>
+          <t>Remote client running on mcu2_1 should be able to register IP address with EthFw. Ping from PC to remote client should work</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -6397,12 +6406,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1097</t>
+          <t>ETHFW-1331</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC: Support for remote core to query if switch R5 firmware has been loaded</t>
+          <t>[EthFw][IPC]IPC:All CPSW subsystem register setting shall be done by means of IPC message to switch R5 core.Not direct register config shall be done on remote cores.</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -6412,7 +6421,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1184,ETHFW-2172</t>
+          <t>ETHFW-1203,ETHFW-2170</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -6427,17 +6436,17 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>For generic kernel driver in mainline, dependency on pre-initialization is not good experience (people use different bootloader, boot sequence etc). So there should be a way to query of firmware is loaded and if not let driver load it from filesystem.</t>
+          <t>IPC:All CPSW subsystem register setting shall be done by means of IPC message to switch R5 core.Not direct register config shall be done on remote cores.</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t>J7 EVM with GESI or QSGMII DB</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check in boot log, remote core should able to query of firmware is loaded or not </t>
+          <t>&lt;To be updated&gt;</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -6457,7 +6466,7 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6496,22 +6505,22 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1058</t>
+          <t>ETHFW-1097</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC:Support for switch configuration from remote core</t>
+          <t>[EthFw][IPC]IPC: Support for remote core to query if switch R5 firmware has been loaded</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1168,ETHFW-2171,ETHFW-2172</t>
+          <t>ETHFW-1184,ETHFW-2172</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -6526,7 +6535,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>IPC:Support for switch configuration from remote core</t>
+          <t>For generic kernel driver in mainline, dependency on pre-initialization is not good experience (people use different bootloader, boot sequence etc). So there should be a way to query of firmware is loaded and if not let driver load it from filesystem.</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -6536,7 +6545,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Should able to configure Switch from all cores</t>
+          <t xml:space="preserve">Check in boot log, remote core should able to query of firmware is loaded or not </t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -6595,22 +6604,22 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-987</t>
+          <t>ETHFW-1058</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC: Integration with CPSW LLD RTOS driver running on RTOS remote cores</t>
+          <t>[EthFw][IPC]IPC:Support for switch configuration from remote core</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement,Requirement,Requirement</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1148,ETHFW-2171</t>
+          <t>ETHFW-1168,ETHFW-2171,ETHFW-2172</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -6625,7 +6634,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware IPC should be integrated with Enet LLD RTOS driver running on RTOS remote cores.</t>
+          <t>IPC:Support for switch configuration from remote core</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -6635,7 +6644,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Should able to run application successfully </t>
+          <t>Should able to configure Switch from all cores</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -6694,22 +6703,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1025</t>
+          <t>ETHFW-987</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>[EthFw][IPC]IPC: Integration with linux virtual driver running on A72 remote core</t>
+          <t>[EthFw][IPC]IPC: Integration with CPSW LLD RTOS driver running on RTOS remote cores</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1143</t>
+          <t>ETHFW-1148,ETHFW-2171</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -6724,7 +6733,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Ethernet Firmware IPC should be integrated with linux virtual netdev driver running on A72 remote core</t>
+          <t>Ethernet Firmware IPC should be integrated with Enet LLD RTOS driver running on RTOS remote cores.</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6793,12 +6802,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1547</t>
+          <t>ETHFW-1025</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>EthFw - Support EthFw as library to enable SDK integration</t>
+          <t>[EthFw][IPC]IPC: Integration with linux virtual driver running on A72 remote core</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -6808,7 +6817,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1119</t>
+          <t>ETHFW-1143</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -6823,20 +6832,17 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ethfw does not have a unified library interface like EthFw_init() that would pull in all dependent libs and perform system initialization. Such an interface would be required to integrate with vision apps.  
-Currently ethFw is an app enabling basic switching, remote config server for virtual clients etc. with switch config server running for getting configuration from the PC client tool.
-Requirement is to support EthFw as an Library for SDK integration. 
- </t>
+          <t>Ethernet Firmware IPC should be integrated with linux virtual netdev driver running on A72 remote core</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with QSGMII or GESI or both daughter boards</t>
+          <t>J7 EVM with GESI Expansion card</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>EthFw server app should be able to link EthFw library and configure CPSW9G switch.</t>
+          <t xml:space="preserve">Should able to run application successfully </t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -6856,7 +6862,7 @@
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -6895,12 +6901,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1405</t>
+          <t>ETHFW-1547</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>EthFW System Test - GPTIMER Driver Integration</t>
+          <t>EthFw - Support EthFw as library to enable SDK integration</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -6910,7 +6916,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-955</t>
+          <t>ETHFW-1119</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6925,17 +6931,20 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][System]Driver Integration:GPTIMER: GPTIMER driver should be integrated</t>
+          <t xml:space="preserve">Ethfw does not have a unified library interface like EthFw_init() that would pull in all dependent libs and perform system initialization. Such an interface would be required to integrate with vision apps.  
+Currently ethFw is an app enabling basic switching, remote config server for virtual clients etc. with switch config server running for getting configuration from the PC client tool.
+Requirement is to support EthFw as an Library for SDK integration. 
+ </t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t>J7 EVM with QSGMII or GESI or both daughter boards</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Confirm packet interrupts occur at periodic 500us interval only when interrupt pacing is enabled. The interrupt pacing is triggered by TImer interrupt</t>
+          <t>EthFw server app should be able to link EthFw library and configure CPSW9G switch.</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -6955,7 +6964,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6994,12 +7003,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1424</t>
+          <t>ETHFW-1405</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>EthFW EMAC OSAL Test - Baremetal implementation</t>
+          <t>EthFW System Test - GPTIMER Driver Integration</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -7009,7 +7018,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-941</t>
+          <t>ETHFW-955</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -7024,7 +7033,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][OS]OSAL:EMAC Osal:Baremetal implementation of EMAL osal interface should be integrated into the switch firmware</t>
+          <t>[EthFW][System]Driver Integration:GPTIMER: GPTIMER driver should be integrated</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -7034,7 +7043,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>Execute cpsw baremetal test app and confirm successful execution</t>
+          <t>Confirm packet interrupts occur at periodic 500us interval only when interrupt pacing is enabled. The interrupt pacing is triggered by TImer interrupt</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -7093,12 +7102,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1344</t>
+          <t>ETHFW-1424</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>EthFW System Test - PMU Driver Integration</t>
+          <t>EthFW EMAC OSAL Test - Baremetal implementation</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -7108,7 +7117,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-937</t>
+          <t>ETHFW-941</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -7123,7 +7132,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][System]Driver Integration:PMU: PMU driver should be integrated</t>
+          <t>[EthFW][OS]OSAL:EMAC Osal:Baremetal implementation of EMAL osal interface should be integrated into the switch firmware</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -7133,7 +7142,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Should be able to get PMU counters for perfomance profiling</t>
+          <t>Execute cpsw baremetal test app and confirm successful execution</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -7192,12 +7201,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1415</t>
+          <t>ETHFW-1344</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>EthFW OS Test - CPSW LLD validation</t>
+          <t>EthFW System Test - PMU Driver Integration</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -7207,7 +7216,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-903</t>
+          <t>ETHFW-937</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -7222,7 +7231,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][OS]OS:cpsw_lld should be validated on split mode variant of TI RTOS config</t>
+          <t>[EthFW][System]Driver Integration:PMU: PMU driver should be integrated</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -7232,7 +7241,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EthFw switching app should run successfully on MCU_2_1 with MCU _2 configured in split mode </t>
+          <t>Should be able to get PMU counters for perfomance profiling</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -7291,12 +7300,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1325</t>
+          <t>ETHFW-1415</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>EthFW System Test - TISCI client Driver Integration</t>
+          <t>EthFW OS Test - CPSW LLD validation</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -7306,7 +7315,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-899</t>
+          <t>ETHFW-903</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -7321,7 +7330,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>[EthFW][System]Driver Integration:TISCI: TISCI client driver should be integrated for DMSC IPC</t>
+          <t>[EthFW][OS]OS:cpsw_lld should be validated on split mode variant of TI RTOS config</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -7331,7 +7340,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm successful execution with DMSC firmware </t>
+          <t xml:space="preserve">EthFw switching app should run successfully on MCU_2_1 with MCU _2 configured in split mode </t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -7390,12 +7399,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1543</t>
+          <t>ETHFW-1325</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EthFw: Support Thumb2 mode on R5F </t>
+          <t>EthFW System Test - TISCI client Driver Integration</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -7405,7 +7414,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-761</t>
+          <t>ETHFW-899</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -7420,29 +7429,17 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>This is a cloned requirement from PRSDK-5804
-Copied description below 
-================
-We have been performing performance benchmarking on R5F using TI ARM compiler on AM65x for Panasonic and broader Motor Drives EE space and have seen R5F performance is significantly better with smaller code size with Thumb2 mode which is a hybrid mode supported on Cortex R5F that generates a mix of 16 bit and 32 bit integers. 
-The TI ARM compiler team that has been support Cortex M and Cortex R devices in connected MCU have recommended use of Thumb2 (code_state=16) instead of ARM mode (code_state=32) and also provide this guidance to customer to optimize Cortex R5 performance.
-[http://processors.wiki.ti.com/index.php/ARM_compiler_optimizations#Tips_for_getting_the_best_performance]
- It appears that current support for PRocessor SDK RTOS software is building all of the R5F code in ARM mode but for non-safety usecases, customer need the option to run code in Thumb2 mode.
-We have performed basic sanity testing of RTOS examples with Thumb2 compiler time option and not seen any functional issues. Can we consider bring this support into PRSDK baseline. 
-*Response from SDO RTOS team for this request:*
-This can be supported. A new Thumb2 R5F target would be required. And we’d have to scrub all existing embedded assembly code to make sure it uses thumb2 instructions
-Discussion with Raghu and Alan DeMars is attached for reference.
-[^RE R5F Compile time flags Thumb2 mode support in TI RTOS for R5F .msg]
-Functional Requirement based on req:CATREQ-2455</t>
+          <t>[EthFW][System]Driver Integration:TISCI: TISCI client driver should be integrated for DMSC IPC</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with QSGMII or GESI or both daughter boards</t>
+          <t>J7 EVM with GESI Expansion card</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>The app should be able to run without any issue to completion and there should be performance improvement compared to the NON-thumb mode when running the SW inerVLAN routing app</t>
+          <t xml:space="preserve">Confirm successful execution with DMSC firmware </t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -7462,7 +7459,7 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -7501,12 +7498,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2523</t>
+          <t>ETHFW-1543</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Ethernet port stats monitoring</t>
+          <t xml:space="preserve">EthFw: Support Thumb2 mode on R5F </t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -7516,12 +7513,12 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2479</t>
+          <t>ETHFW-761</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+          <t>j721e-evm,j7200-evm</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -7531,17 +7528,29 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Verify that ETHFW is able to periodically monitor CPSW statistics and can notify ETHFW server application of such events.</t>
+          <t>This is a cloned requirement from PRSDK-5804
+Copied description below 
+================
+We have been performing performance benchmarking on R5F using TI ARM compiler on AM65x for Panasonic and broader Motor Drives EE space and have seen R5F performance is significantly better with smaller code size with Thumb2 mode which is a hybrid mode supported on Cortex R5F that generates a mix of 16 bit and 32 bit integers. 
+The TI ARM compiler team that has been support Cortex M and Cortex R devices in connected MCU have recommended use of Thumb2 (code_state=16) instead of ARM mode (code_state=32) and also provide this guidance to customer to optimize Cortex R5 performance.
+[http://processors.wiki.ti.com/index.php/ARM_compiler_optimizations#Tips_for_getting_the_best_performance]
+ It appears that current support for PRocessor SDK RTOS software is building all of the R5F code in ARM mode but for non-safety usecases, customer need the option to run code in Thumb2 mode.
+We have performed basic sanity testing of RTOS examples with Thumb2 compiler time option and not seen any functional issues. Can we consider bring this support into PRSDK baseline. 
+*Response from SDO RTOS team for this request:*
+This can be supported. A new Thumb2 R5F target would be required. And we’d have to scrub all existing embedded assembly code to make sure it uses thumb2 instructions
+Discussion with Raghu and Alan DeMars is attached for reference.
+[^RE R5F Compile time flags Thumb2 mode support in TI RTOS for R5F .msg]
+Functional Requirement based on req:CATREQ-2455</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>J721E/J7200/J784S4 EVM.</t>
+          <t>J7 EVM with QSGMII or GESI or both daughter boards</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Ethernet stats monitor callback should be called when a stats counter increase since previous periodic read.</t>
+          <t>The app should be able to run without any issue to completion and there should be performance improvement compared to the NON-thumb mode when running the SW inerVLAN routing app</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -7561,7 +7570,7 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -7600,12 +7609,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2524</t>
+          <t>ETHFW-2523</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Host port stats monitoring</t>
+          <t>EthFw: Ethernet port stats monitoring</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -7615,7 +7624,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2480</t>
+          <t>ETHFW-2479</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -7630,7 +7639,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Verify that ETHFW is able to periodically monitor CPSW host port statistics and can notify ETHFW server application of such events.</t>
+          <t>Verify that ETHFW is able to periodically monitor CPSW statistics and can notify ETHFW server application of such events.</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -7640,7 +7649,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>Host stats monitor callback should be called when a stats counter increase since previous periodic read.</t>
+          <t>Ethernet stats monitor callback should be called when a stats counter increase since previous periodic read.</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -7699,12 +7708,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2522</t>
+          <t>ETHFW-2524</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Trace logging level (runtime)</t>
+          <t>EthFw: Host port stats monitoring</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -7714,7 +7723,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2477</t>
+          <t>ETHFW-2480</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -7729,7 +7738,7 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Verify ETHFW log levels can be set at runtime via EthFwTrace_setLevel().</t>
+          <t>Verify that ETHFW is able to periodically monitor CPSW host port statistics and can notify ETHFW server application of such events.</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -7739,7 +7748,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Log level shall be changed to the level selected by the application at runtime.</t>
+          <t>Host stats monitor callback should be called when a stats counter increase since previous periodic read.</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -7798,12 +7807,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2521</t>
+          <t>ETHFW-2522</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Trace logging level (compile-time)</t>
+          <t>EthFw: Trace logging level (runtime)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -7828,7 +7837,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Verify ETHFW log levels can be set at compile time via ETHFW_CFG_TRACE_LEVEL configuration parameter.</t>
+          <t>Verify ETHFW log levels can be set at runtime via EthFwTrace_setLevel().</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -7838,7 +7847,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>Build-time log level shall be set according to the build configuration parameter ETHFW_CFG_TRACE_LEVEL.</t>
+          <t>Log level shall be changed to the level selected by the application at runtime.</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -7897,12 +7906,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2520</t>
+          <t>ETHFW-2521</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Traces with unique error code</t>
+          <t>EthFw: Trace logging level (compile-time)</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -7912,7 +7921,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2489</t>
+          <t>ETHFW-2477</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -7927,21 +7936,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Verify that the external trace function gets called with a unique error code when ETHFW encounters an error condition at runtime.
-Reference unique error callback:
-{code:c}
-void EthApp_extTraceFunc(uint32_t errCode)
-{
-  appLogPrintf("Error code: %x\n", errCode);
-}
-/* Trace configuration */
-static EthFwTrace_Cfg gEthApp_traceCfg =
-{
-  .print        = appLogPrintf,
-  .traceTsFunc  = NULL,
-  .extTraceFunc = EthApp_extTraceFunc,
-};
-EthFwTrace_init(&amp;gEthApp_traceCfg); {code}</t>
+          <t>Verify ETHFW log levels can be set at compile time via ETHFW_CFG_TRACE_LEVEL configuration parameter.</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -7951,7 +7946,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>EthFw unique errors shall be logged using the provided callback function.</t>
+          <t>Build-time log level shall be set according to the build configuration parameter ETHFW_CFG_TRACE_LEVEL.</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -8010,12 +8005,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2519</t>
+          <t>ETHFW-2520</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>EthFw: Timestamped logs/traces</t>
+          <t>EthFw: Traces with unique error code</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -8025,7 +8020,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2478</t>
+          <t>ETHFW-2489</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -8040,28 +8035,21 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Verify that ETHFW tracing feature supports timestamping of logs/traces using an timestamp provider set by application.
-Reference timestamp provider:
-{code:c}
-#define SEC_TO_USEC (1000000ULL)
-static uint64_t EthApp_traceTs(void)
-{
-  static uint64_t ts = 0ULL;
-  TickType_t tickCnt;
-  uint64_t tickUsecs;
-  tickUsecs = SEC_TO_USEC / uint64_t)configTICK_RATE_HZ;
-  tickCnt = xTaskGetTickCount();
-  ts = (uint64_t)tickCnt * tickUsecs;
-  return ts;
-}
-/* Trace configuration */
-static EthFwTrace_Cfg gEthApp_traceCfg =
-{
-  .print        = appLogPrintf,
-  .traceTsFunc  = EthApp_traceTs,
-  .extTraceFunc = NULL,
-};
-EthFwTrace_init(&amp;gEthApp_traceCfg);{code}</t>
+          <t>Verify that the external trace function gets called with a unique error code when ETHFW encounters an error condition at runtime.
+Reference unique error callback:
+{code:c}
+void EthApp_extTraceFunc(uint32_t errCode)
+{
+  appLogPrintf("Error code: %x\n", errCode);
+}
+/* Trace configuration */
+static EthFwTrace_Cfg gEthApp_traceCfg =
+{
+  .print        = appLogPrintf,
+  .traceTsFunc  = NULL,
+  .extTraceFunc = EthApp_extTraceFunc,
+};
+EthFwTrace_init(&amp;gEthApp_traceCfg); {code}</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -8071,7 +8059,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>ETHFW traces shall be printed with a timestamp.</t>
+          <t>EthFw unique errors shall be logged using the provided callback function.</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -8120,32 +8108,32 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2526</t>
+          <t>ETHFW-2366</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>EthFw Reset Recovery Test Plan</t>
+          <t>ETHFW 9.x Release Test Plan (j721e)</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2515</t>
+          <t>ETHFW-2519</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>EthFw: FreeRTOS Reset Recovery test on EthFw standalone</t>
+          <t>EthFw: Timestamped logs/traces</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2162,ETHFW-2160,ETHFW-2164,ETHFW-2163,ETHFW-2167,ETHFW-2161</t>
+          <t>ETHFW-2478</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -8160,18 +8148,38 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw.
-</t>
+          <t>Verify that ETHFW tracing feature supports timestamping of logs/traces using an timestamp provider set by application.
+Reference timestamp provider:
+{code:c}
+#define SEC_TO_USEC (1000000ULL)
+static uint64_t EthApp_traceTs(void)
+{
+  static uint64_t ts = 0ULL;
+  TickType_t tickCnt;
+  uint64_t tickUsecs;
+  tickUsecs = SEC_TO_USEC / uint64_t)configTICK_RATE_HZ;
+  tickCnt = xTaskGetTickCount();
+  ts = (uint64_t)tickCnt * tickUsecs;
+  return ts;
+}
+/* Trace configuration */
+static EthFwTrace_Cfg gEthApp_traceCfg =
+{
+  .print        = appLogPrintf,
+  .traceTsFunc  = EthApp_traceTs,
+  .extTraceFunc = NULL,
+};
+EthFwTrace_init(&amp;gEthApp_traceCfg);{code}</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>J7 EVM with GESI Expansion card</t>
+          <t>J721E/J7200/J784S4 EVM.</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Recovery should be successful and post recovery packet transmission(ping/iperf should work)</t>
+          <t>ETHFW traces shall be printed with a timestamp.</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -8230,16 +8238,24 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2529</t>
+          <t>ETHFW-2515</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>EthFw: SafeRTOS Reset Recovery test on EthFw standalone</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
+          <t>EthFw: FreeRTOS Reset Recovery test on EthFw standalone</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2162,ETHFW-2160,ETHFW-2164,ETHFW-2163,ETHFW-2167,ETHFW-2161</t>
+        </is>
+      </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
           <t>j721e-evm,j7200-evm,j784s4-evm</t>
@@ -8252,7 +8268,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw.
+          <t xml:space="preserve">Test Reset recovery on EthFw.
 </t>
         </is>
       </c>
@@ -8322,12 +8338,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2528</t>
+          <t>ETHFW-2529</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>EthFw: SafeRTOS: Reset Recovery test on EthFw + MCAL Client</t>
+          <t>EthFw: SafeRTOS Reset Recovery test on EthFw standalone</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr"/>
@@ -8344,7 +8360,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw with MCAL client
+          <t xml:space="preserve">Test Reset recovery on EthFw.
 </t>
         </is>
       </c>
@@ -8414,12 +8430,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2527</t>
+          <t>ETHFW-2528</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>EthFw: FreeRTOS: Reset Recovery test on EthFw + MCAL Client</t>
+          <t>EthFw: SafeRTOS: Reset Recovery test on EthFw + MCAL Client</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr"/>
@@ -8436,7 +8452,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw with MCAL client
+          <t xml:space="preserve">Test Reset recovery on EthFw with MCAL client
 </t>
         </is>
       </c>
@@ -8506,12 +8522,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2533</t>
+          <t>ETHFW-2527</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>EthFw: SafeRTOS: Reset Recovery test on EthFw + RTOS Client</t>
+          <t>EthFw: FreeRTOS: Reset Recovery test on EthFw + MCAL Client</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr"/>
@@ -8528,7 +8544,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw with RTOS client
+          <t xml:space="preserve">Test Reset recovery on EthFw with MCAL client
 </t>
         </is>
       </c>
@@ -8598,12 +8614,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2532</t>
+          <t>ETHFW-2533</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>EthFw: FreeRTOS: Reset Recovery test on EthFw + RTOS Client</t>
+          <t>EthFw: SafeRTOS: Reset Recovery test on EthFw + RTOS Client</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr"/>
@@ -8620,7 +8636,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw with RTOS client
+          <t xml:space="preserve">Test Reset recovery on EthFw with RTOS client
 </t>
         </is>
       </c>
@@ -8690,12 +8706,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2531</t>
+          <t>ETHFW-2532</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>EthFw: FreeRTOS: Reset Recovery test on EthFw + Linux Client</t>
+          <t>EthFw: FreeRTOS: Reset Recovery test on EthFw + RTOS Client</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr"/>
@@ -8712,7 +8728,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw with Linux client
+          <t xml:space="preserve">Test Reset recovery on EthFw with RTOS client
 </t>
         </is>
       </c>
@@ -8782,12 +8798,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2530</t>
+          <t>ETHFW-2531</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>EthFw: SafeRTOS: Reset Recovery test on EthFw + Linux Client</t>
+          <t>EthFw: FreeRTOS: Reset Recovery test on EthFw + Linux Client</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr"/>
@@ -8804,7 +8820,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw with Linux client
+          <t xml:space="preserve">Test Reset recovery on EthFw with Linux client
 </t>
         </is>
       </c>
@@ -8874,12 +8890,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2534</t>
+          <t>ETHFW-2530</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>EthFw: FreeRTOS Reset Recovery Robust test</t>
+          <t>EthFw: SafeRTOS: Reset Recovery test on EthFw + Linux Client</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr"/>
@@ -8896,7 +8912,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw by triggering multiple iterations of recovery
+          <t xml:space="preserve">Test Reset recovery on EthFw with Linux client
 </t>
         </is>
       </c>
@@ -8966,12 +8982,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2535</t>
+          <t>ETHFW-2534</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>EthFw: SafeRTOS Reset Recovery Robust test</t>
+          <t>EthFw: FreeRTOS Reset Recovery Robust test</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr"/>
@@ -8988,7 +9004,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Reset recovery on EthFw by triggering multiple iterations of recovery
+          <t xml:space="preserve">Test Reset recovery on EthFw by triggering multiple iterations of recovery
 </t>
         </is>
       </c>
@@ -9045,9 +9061,101 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2526</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>EthFw Reset Recovery Test Plan</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2535</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>EthFw: SafeRTOS Reset Recovery Robust test</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Reset recovery on EthFw by triggering multiple iterations of recovery
+</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>J7 EVM with GESI Expansion card</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Recovery should be successful and post recovery packet transmission(ping/iperf should work)</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2505</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW 9.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="inlineStr"/>
+      <c r="T78" s="3" t="inlineStr"/>
+      <c r="U78" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U77"/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <autoFilter ref="A1:U78"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -9060,11 +9168,11 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="16"/>
-    <col customWidth="1" max="2" min="2" width="23"/>
-    <col customWidth="1" max="3" min="3" width="67"/>
-    <col customWidth="1" max="4" min="4" width="30"/>
-    <col customWidth="1" max="5" min="5" width="30"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10007,14 +10115,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A35:A42"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B38:B42"/>
     <mergeCell ref="A2:A34"/>
-    <mergeCell ref="A35:A42"/>
-    <mergeCell ref="B38:B42"/>
     <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B13:B23"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -10027,10 +10135,10 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="12"/>
-    <col customWidth="1" max="2" min="2" width="12"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="100"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10254,6 +10362,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/test_report/ethfw_testreport_j721e.xlsx
+++ b/docs/test_report/ethfw_testreport_j721e.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Test Strategy Compliance'!$A$1:$E$5</definedName>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Test Plan | Execution Report'!$A$1:$U$182</definedName>
+    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">'Test Plan | Execution Report'!$A$1:$U$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2024-08-07 04:09:19.725652-05:00 CDT</t>
+          <t>2024-11-25 04:52:36.373709-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="7" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1434,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U182"/>
+  <dimension ref="A1:U187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="17"/>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -3661,12 +3661,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -3762,12 +3762,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -3964,12 +3964,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4065,12 +4065,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -4570,12 +4570,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -4686,12 +4686,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -4906,12 +4906,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -4999,12 +4999,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -5323,12 +5323,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -5515,12 +5515,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -5791,19 +5791,27 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2974</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW: RTOS: Reset recovery fails with RTOS client</t>
+        </is>
+      </c>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5891,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -5976,19 +5984,19 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -6070,19 +6078,19 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6170,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -6254,12 +6262,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -6360,12 +6368,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -6465,12 +6473,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -6571,12 +6579,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -6676,12 +6684,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -6780,12 +6788,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -6884,12 +6892,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -6988,12 +6996,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -7093,12 +7101,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -7199,12 +7207,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -7304,12 +7312,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -7410,12 +7418,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -7514,12 +7522,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -7616,12 +7624,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -7722,12 +7730,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -7830,12 +7838,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -7938,12 +7946,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -8044,12 +8052,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -8145,12 +8153,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -8248,12 +8256,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -8347,12 +8355,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -8450,12 +8458,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -8549,12 +8557,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -8648,12 +8656,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -8747,12 +8755,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -8850,12 +8858,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -8951,12 +8959,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -9050,12 +9058,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -9155,12 +9163,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -9254,12 +9262,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -9353,12 +9361,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -9452,12 +9460,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -9551,12 +9559,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -9650,12 +9658,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -9752,12 +9760,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -9851,12 +9859,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -9950,12 +9958,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -10049,12 +10057,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -10148,12 +10156,12 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
@@ -10247,12 +10255,12 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
@@ -10358,12 +10366,12 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
@@ -10457,12 +10465,12 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
@@ -10556,12 +10564,12 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
@@ -10655,12 +10663,12 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
@@ -10754,12 +10762,12 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
@@ -10867,12 +10875,12 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
@@ -10987,12 +10995,12 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
@@ -11090,12 +11098,12 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
@@ -11196,12 +11204,12 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
@@ -11302,12 +11310,12 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
@@ -11404,12 +11412,12 @@
       </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr"/>
@@ -11505,12 +11513,12 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr"/>
@@ -11608,12 +11616,12 @@
       </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr"/>
@@ -11711,12 +11719,12 @@
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr"/>
@@ -11815,12 +11823,12 @@
       </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr"/>
@@ -11918,12 +11926,12 @@
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr"/>
@@ -12019,24 +12027,16 @@
       </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R104" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
-        </is>
-      </c>
-      <c r="S104" s="3" t="inlineStr">
-        <is>
-          <t>ETHFW-2575</t>
-        </is>
-      </c>
-      <c r="T104" s="3" t="inlineStr">
-        <is>
-          <t>CPSW error flags are not getting updated in UDMA host packet descriptor</t>
-        </is>
-      </c>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S104" s="3" t="inlineStr"/>
+      <c r="T104" s="3" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
@@ -12129,12 +12129,12 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr"/>
@@ -12231,12 +12231,12 @@
       </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S106" s="3" t="inlineStr"/>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S107" s="3" t="inlineStr"/>
@@ -12435,12 +12435,12 @@
       </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr"/>
@@ -12537,12 +12537,12 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S109" s="3" t="inlineStr"/>
@@ -12639,12 +12639,12 @@
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R110" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr"/>
@@ -12741,12 +12741,12 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr"/>
@@ -12843,12 +12843,12 @@
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
@@ -12945,12 +12945,12 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr"/>
@@ -13047,12 +13047,12 @@
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr"/>
@@ -13149,12 +13149,12 @@
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S115" s="3" t="inlineStr"/>
@@ -13251,12 +13251,12 @@
       </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R116" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S116" s="3" t="inlineStr"/>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R117" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S117" s="3" t="inlineStr"/>
@@ -13455,12 +13455,12 @@
       </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R118" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S118" s="3" t="inlineStr"/>
@@ -13557,12 +13557,12 @@
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R119" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S119" s="3" t="inlineStr"/>
@@ -13659,12 +13659,12 @@
       </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R120" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr"/>
@@ -13761,12 +13761,12 @@
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R121" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S121" s="3" t="inlineStr"/>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R122" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S122" s="3" t="inlineStr"/>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R123" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S123" s="3" t="inlineStr"/>
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R124" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S124" s="3" t="inlineStr"/>
@@ -14169,12 +14169,12 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R125" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S125" s="3" t="inlineStr"/>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R126" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S126" s="3" t="inlineStr"/>
@@ -14373,12 +14373,12 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R127" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S127" s="3" t="inlineStr"/>
@@ -14475,12 +14475,12 @@
       </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R128" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S128" s="3" t="inlineStr"/>
@@ -14577,12 +14577,12 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R129" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S129" s="3" t="inlineStr"/>
@@ -14679,12 +14679,12 @@
       </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R130" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S130" s="3" t="inlineStr"/>
@@ -14781,12 +14781,12 @@
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R131" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S131" s="3" t="inlineStr"/>
@@ -14883,12 +14883,12 @@
       </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R132" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S132" s="3" t="inlineStr"/>
@@ -14985,12 +14985,12 @@
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R133" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S133" s="3" t="inlineStr"/>
@@ -15087,12 +15087,12 @@
       </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R134" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S134" s="3" t="inlineStr"/>
@@ -15189,12 +15189,12 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R135" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S135" s="3" t="inlineStr"/>
@@ -15291,12 +15291,12 @@
       </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R136" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S136" s="3" t="inlineStr"/>
@@ -15393,12 +15393,12 @@
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R137" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S137" s="3" t="inlineStr"/>
@@ -15495,12 +15495,12 @@
       </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr"/>
@@ -15597,12 +15597,12 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R139" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S139" s="3" t="inlineStr"/>
@@ -15699,12 +15699,12 @@
       </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S140" s="3" t="inlineStr"/>
@@ -15801,12 +15801,12 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R141" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S141" s="3" t="inlineStr"/>
@@ -15903,12 +15903,12 @@
       </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R142" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S142" s="3" t="inlineStr"/>
@@ -16005,12 +16005,12 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R143" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S143" s="3" t="inlineStr"/>
@@ -16107,12 +16107,12 @@
       </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr"/>
@@ -16209,12 +16209,12 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R145" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S145" s="3" t="inlineStr"/>
@@ -16311,12 +16311,12 @@
       </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R146" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S146" s="3" t="inlineStr"/>
@@ -16413,12 +16413,12 @@
       </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R147" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S147" s="3" t="inlineStr"/>
@@ -16515,12 +16515,12 @@
       </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R148" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S148" s="3" t="inlineStr"/>
@@ -16617,12 +16617,12 @@
       </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R149" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S149" s="3" t="inlineStr"/>
@@ -16719,12 +16719,12 @@
       </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr"/>
@@ -16821,12 +16821,12 @@
       </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R151" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S151" s="3" t="inlineStr"/>
@@ -16923,12 +16923,12 @@
       </c>
       <c r="Q152" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R152" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S152" s="3" t="inlineStr"/>
@@ -17025,12 +17025,12 @@
       </c>
       <c r="Q153" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R153" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S153" s="3" t="inlineStr"/>
@@ -17127,12 +17127,12 @@
       </c>
       <c r="Q154" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr"/>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="Q155" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R155" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S155" s="3" t="inlineStr"/>
@@ -17331,12 +17331,12 @@
       </c>
       <c r="Q156" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S156" s="3" t="inlineStr"/>
@@ -17433,12 +17433,12 @@
       </c>
       <c r="Q157" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R157" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S157" s="3" t="inlineStr"/>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="Q158" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R158" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S158" s="3" t="inlineStr"/>
@@ -17637,12 +17637,12 @@
       </c>
       <c r="Q159" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R159" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S159" s="3" t="inlineStr"/>
@@ -17739,12 +17739,12 @@
       </c>
       <c r="Q160" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R160" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S160" s="3" t="inlineStr"/>
@@ -17841,12 +17841,12 @@
       </c>
       <c r="Q161" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R161" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S161" s="3" t="inlineStr"/>
@@ -17943,12 +17943,12 @@
       </c>
       <c r="Q162" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R162" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S162" s="3" t="inlineStr"/>
@@ -18045,12 +18045,12 @@
       </c>
       <c r="Q163" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr"/>
@@ -18147,12 +18147,12 @@
       </c>
       <c r="Q164" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr"/>
@@ -18249,12 +18249,12 @@
       </c>
       <c r="Q165" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr"/>
@@ -18351,12 +18351,12 @@
       </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R166" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S166" s="3" t="inlineStr"/>
@@ -18453,12 +18453,12 @@
       </c>
       <c r="Q167" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr"/>
@@ -18555,12 +18555,12 @@
       </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R168" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S168" s="3" t="inlineStr"/>
@@ -18657,12 +18657,12 @@
       </c>
       <c r="Q169" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R169" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S169" s="3" t="inlineStr"/>
@@ -18759,12 +18759,12 @@
       </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R170" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S170" s="3" t="inlineStr"/>
@@ -18861,12 +18861,12 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R171" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S171" s="3" t="inlineStr"/>
@@ -18963,12 +18963,12 @@
       </c>
       <c r="Q172" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr"/>
@@ -19065,12 +19065,12 @@
       </c>
       <c r="Q173" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R173" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr"/>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="Q174" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R174" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S174" s="3" t="inlineStr"/>
@@ -19269,12 +19269,12 @@
       </c>
       <c r="Q175" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R175" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S175" s="3" t="inlineStr"/>
@@ -19371,12 +19371,12 @@
       </c>
       <c r="Q176" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R176" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S176" s="3" t="inlineStr"/>
@@ -19473,12 +19473,12 @@
       </c>
       <c r="Q177" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R177" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S177" s="3" t="inlineStr"/>
@@ -19575,12 +19575,12 @@
       </c>
       <c r="Q178" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R178" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S178" s="3" t="inlineStr"/>
@@ -19677,12 +19677,12 @@
       </c>
       <c r="Q179" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S179" s="3" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
       </c>
       <c r="Q180" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R180" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S180" s="3" t="inlineStr"/>
@@ -19881,12 +19881,12 @@
       </c>
       <c r="Q181" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R181" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S181" s="3" t="inlineStr"/>
@@ -19983,12 +19983,12 @@
       </c>
       <c r="Q182" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2827</t>
+          <t>ETHFW-2969</t>
         </is>
       </c>
       <c r="R182" s="3" t="inlineStr">
         <is>
-          <t>ETHFW 10.0 Release Test Run (j721e)</t>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
         </is>
       </c>
       <c r="S182" s="3" t="inlineStr"/>
@@ -19999,8 +19999,534 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2971</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW VLAN test plan</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2892</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Shared multicast test with VLAN</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Requirement,Requirement</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2895,ETHFW-2891</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>j784s4-evm</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>Shared multicast is a traffic that is supposed to be reached to multiple clients post registration.
+This test exercises the same with and without VLAN.
+As we lwip bridge does not support VLAN, shared multicast should reach all the clients who have reigstered with that multicast address irrespective of VLAN in NON-VEPA case.
+Similarly shared multicast should reach only to the specific client who have registered with that multicast address with VLAN. As we are honoring VLAN with shared multicast on devices where VEPA is enabled.</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>1. Join VLAN from client1 and another VLAN from client2 (do vlan_join from Linux client or add an instruction in RTOS client)
+2. Register to same shared multicast address from client1 and client2 but with different VLANs.
+3. Send a packet with dst mac as shared multicast address with different combinations (i.e. with VLAN 0, client1's VLAN, client2's VLAN and unknown VLAN).
+3. Check packet receive at clients. See the success criteria for details.</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>Shared multicast should reach all the clients who have reigstered with that multicast address irrespective of VLAN in NON-VEPA case.
+Shared multicast should reach only to the specific client who have registered with that multicast address with VLAN. As we are honoring VLAN with shared multicast on devices where VEPA is enabled.</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2969</t>
+        </is>
+      </c>
+      <c r="R183" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S183" s="3" t="inlineStr"/>
+      <c r="T183" s="3" t="inlineStr"/>
+      <c r="U183" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2971</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW VLAN test plan</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2876</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>VLANs honored with unicast packets with multiple clients</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2895</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>VLAN tagged unicast packets should only be reached to the client if the client has joined that VLAN or if any other client has joined that VLAN else should be dropped.
+When multiple clients join different VLAN and we send a packet of 1 client's mac address say M1 with another client's VLAN say V2, then still packet is being received by M1 client. This has been taken as a known limitation so that we use less number of ALE and Classifier entires out of box. Note that not all VLAN packets will be received by M1. VLAN packets who's unicast address is M1 and VLAN registered by M1 or any other client will be received by M1. Unknown VLAN tagged packets with source mac address as M1 will still not be received by M1. This has been ensured excluding host port from unknown VLAN member list mask.</t>
+        </is>
+      </c>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>1. Join VLAN 1024 from client C1, and VLAN 1025 from client C2. (do vlan_join from Linux client or add an instruction in RTOS client)
+2. Send unicast packets of C1's MAC address but with VLAN 1025 (C2's VLAN) (use packETH)
+3. Check packet receive at client, and observe that packet should reach to any client (due to known limitation)
+4. Make sure you test the reverse and C1 with 1024 and C2 with 1025 vlan as well (i.e. correct VLAN)
+5. Send an uknown VLAN (say 102) with C1's mac address. Packet should NOT be reached to C1. Do that same with C2 as well.
+6. Packets with only registered VLAN should be propagated to host port, that too post any client joins that VLAN.</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>Check packet receive at client, and observe that packet should NOT reach to any client</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="Q184" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2969</t>
+        </is>
+      </c>
+      <c r="R184" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S184" s="3" t="inlineStr"/>
+      <c r="T184" s="3" t="inlineStr"/>
+      <c r="U184" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2971</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW VLAN test plan</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2875</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>VLAN Broadcast packets duplicated to clients in VEPA</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2895</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>j784s4-evm</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>VLAN Broadcast packets should only be duplicated to clients who have joined that VLAN. This functionality should work with VEPA on J784S4.</t>
+        </is>
+      </c>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t>1. Join VLAN from client (do vlan_join from Linux client or add an instruction in RTOS client)
+2. Send a Broadcast + VLAN of above joined packet to any of switch Port (use packETH)
+3. Check packet receive at client, and observe that packet should reach to clients
+4. Make sure that other external ports which are not part of that VLAN should not receive those packets (use wireshark to track that)</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>Check packet receive at client, and observe that packet should reach to clients
+Make sure that other external ports which are not part of that VLAN should not receive those packets (use wireshark to track that)</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2969</t>
+        </is>
+      </c>
+      <c r="R185" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S185" s="3" t="inlineStr"/>
+      <c r="T185" s="3" t="inlineStr"/>
+      <c r="U185" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2971</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW VLAN test plan</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2878</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>ARP VLAN packets replied by EthFw (proxy arp)</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2895</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>When we send VLAN ARP packet i.e. a VLAN Broadcast packet post a VLAN_JOIN from a client,
+ARP packets reply should come from EthFw.</t>
+        </is>
+      </c>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>1. Join VLAN from client (do vlan_join say 1025 from Linux client or add an instruction in RTOS client)
+2. Send a ARP + VLAN of above joined packet to any of switch Port (use packETH)
+3. Check packet receive at ethfw handle ARP rx packet function
+4. Make sure that EthFw replies to this ARP + VLAN
+5. See the reply comes back on external port (use wireshark)</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>ARP + VLAN packets reply should come from EthFw.</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O186" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2969</t>
+        </is>
+      </c>
+      <c r="R186" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S186" s="3" t="inlineStr"/>
+      <c r="T186" s="3" t="inlineStr"/>
+      <c r="U186" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2971</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW VLAN test plan</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2890</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Exclusive Multicast Address test</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2895</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>j721e-evm,j7200-evm,j784s4-evm</t>
+        </is>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>Exclusive multicast address M to be exclusive irrespective of VLAN
+We are stopping other clients to join M post 1 client joins M
+In case when client registers exclusive multicast in a VLAN,
+we are still registering it only at mac address level and ignoring the VLAN provided.</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>1. Join exclusive multicast from client C (do ip  maddr add from Linux client or add an instruction in RTOS client)
+2. ip maddr add 01:80:c2:00:00:07 dev eth2
+3. Make sure that exclusive multicast gets added
+4. Delete the exclusive mcast addr: ip maddr del 01:80:c2:00:00:07 dev eth2
+5. Make sure that it gets deleted
+6. Do multiple additions from different clients on the same address
+7. Similarly do multiple deletions as well. Make sure you get error on multiple additions and deletions from firmware.</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>Addition and deletion of exclusive multicast should work fine. Multiple addition or deletion should throw an error.</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O187" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>EthFw</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2969</t>
+        </is>
+      </c>
+      <c r="R187" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW 10.1 Release Test Run (j721e)</t>
+        </is>
+      </c>
+      <c r="S187" s="3" t="inlineStr"/>
+      <c r="T187" s="3" t="inlineStr"/>
+      <c r="U187" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U182"/>
+  <autoFilter ref="A1:U187"/>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>

--- a/docs/test_report/ethfw_testreport_j721e.xlsx
+++ b/docs/test_report/ethfw_testreport_j721e.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0512659\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0512659\Desktop\EthFw 11.2 Collaterals\Test Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE272E9-2319-472B-8585-A8DA9CE38712}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9730C0D1-8D64-4F3B-AEF1-38DDB0C16040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="1" r:id="rId1"/>
@@ -105,13 +105,13 @@
     <t>Report generated on</t>
   </si>
   <si>
-    <t>ETHFW-3389</t>
+    <t>ETHFW-3506</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>2025-08-21 06:17:11.849634-05:00 CDT</t>
+    <t>2025-12-09 05:50:16.785030-06:00 CDT</t>
   </si>
   <si>
     <t>Test Level | Overall Status</t>
@@ -141,10 +141,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>77</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>81</t>
@@ -162,10 +162,10 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>107</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>108</t>
@@ -189,19 +189,19 @@
     <t>0%</t>
   </si>
   <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>2%</t>
+    <t>95%</t>
+  </si>
+  <si>
+    <t>5%</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>3%</t>
+    <t>99%</t>
+  </si>
+  <si>
+    <t>1%</t>
   </si>
   <si>
     <t>Test Type</t>
@@ -333,7 +333,7 @@
     <t>EthFw</t>
   </si>
   <si>
-    <t>ETHFW 11.1 Release Test Run (j721e)</t>
+    <t>ETHFW 11.2 Release Test Run (j721e)</t>
   </si>
   <si>
     <t>ETHFW-1010</t>
@@ -3792,16 +3792,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3835,19 +3833,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -3878,7 +3869,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3901,16 +3892,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3928,7 +3916,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4245,18 +4233,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -6637,7 +6625,7 @@
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="11" t="s">
+      <c r="U29" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6824,7 +6812,7 @@
       <c r="T32" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="U32" s="10" t="s">
+      <c r="U32" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7678,7 +7666,7 @@
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
-      <c r="U46" s="11" t="s">
+      <c r="U46" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8959,7 +8947,7 @@
       </c>
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
-      <c r="U67" s="11" t="s">
+      <c r="U67" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10000,7 +9988,7 @@
       <c r="T84" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="U84" s="10" t="s">
+      <c r="U84" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -10370,7 +10358,7 @@
       <c r="T90" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="U90" s="10" t="s">
+      <c r="U90" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -11224,7 +11212,7 @@
       </c>
       <c r="S104" s="1"/>
       <c r="T104" s="1"/>
-      <c r="U104" s="11" t="s">
+      <c r="U104" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15986,7 +15974,7 @@
       <c r="T182" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="U182" s="10" t="s">
+      <c r="U182" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -16600,7 +16588,7 @@
       <c r="T192" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="U192" s="10" t="s">
+      <c r="U192" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -16722,7 +16710,7 @@
       </c>
       <c r="S194" s="1"/>
       <c r="T194" s="1"/>
-      <c r="U194" s="11" t="s">
+      <c r="U194" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16822,10 +16810,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>979</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -16839,8 +16827,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="10" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -16854,8 +16842,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -16869,8 +16857,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -16884,8 +16872,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="10" t="s">
         <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -16899,8 +16887,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="10" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -16914,8 +16902,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="10" t="s">
         <v>987</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -16929,14 +16917,14 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="10" t="s">
         <v>74</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -16944,8 +16932,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -16959,8 +16947,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="9" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="10" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -16974,8 +16962,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="9" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="10" t="s">
         <v>77</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -16989,14 +16977,14 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16" t="s">
         <v>57</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -17004,12 +16992,12 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E14" s="7" t="s">
@@ -17017,12 +17005,12 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E15" s="7" t="s">
@@ -17030,12 +17018,12 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="17"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E16" s="7" t="s">
@@ -17043,12 +17031,12 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -17056,12 +17044,12 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="17"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E18" s="7" t="s">
@@ -17069,12 +17057,12 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="17"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -17082,12 +17070,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="17"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -17095,12 +17083,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E21" s="7" t="s">
@@ -17108,12 +17096,12 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="17"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -17121,12 +17109,12 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E23" s="7" t="s">
@@ -17134,14 +17122,14 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16" t="s">
         <v>1005</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E24" s="7" t="s">
@@ -17149,12 +17137,12 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -17162,12 +17150,12 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -17175,12 +17163,12 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -17188,27 +17176,27 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="9" t="s">
         <v>990</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="9" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="17"/>
+      <c r="B29" s="10" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E29" s="7" t="s">
@@ -17216,14 +17204,14 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
-      <c r="B30" s="17" t="s">
+      <c r="A30" s="17"/>
+      <c r="B30" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -17231,12 +17219,12 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E31" s="7" t="s">
@@ -17244,12 +17232,12 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E32" s="7" t="s">
@@ -17257,12 +17245,12 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="16"/>
       <c r="C33" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="9" t="s">
         <v>990</v>
       </c>
       <c r="E33" s="7" t="s">
@@ -17270,25 +17258,25 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="17"/>
+      <c r="B34" s="10" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="9" t="s">
         <v>990</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="9" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="15" t="s">
         <v>1017</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -17302,8 +17290,8 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="15"/>
+      <c r="B36" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -17317,8 +17305,8 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="15"/>
+      <c r="B37" s="10" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -17332,8 +17320,8 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="16" t="s">
         <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -17347,8 +17335,8 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
-      <c r="B39" s="17"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="16"/>
       <c r="C39" s="1" t="s">
         <v>1022</v>
       </c>
@@ -17360,8 +17348,8 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="1" t="s">
         <v>1023</v>
       </c>
@@ -17373,8 +17361,8 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="1" t="s">
         <v>1024</v>
       </c>
@@ -17386,8 +17374,8 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="1" t="s">
         <v>1025</v>
       </c>
